--- a/docs/export/templates/SN102-2024-In-kind.xlsx
+++ b/docs/export/templates/SN102-2024-In-kind.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\home\amice13\GIT\RAIS-Plus\front\public\export\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2569F95D-C660-4309-95A1-9569A9905DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9CC137-CE7A-4F77-BC7B-AF9043B1172B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{0D83F5B8-BFFE-4C84-84F2-873EAE6BAEAC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="213">
   <si>
     <t>PARTNER NFI DISTRIBUTION REPORT</t>
   </si>
@@ -771,6 +771,12 @@
   </si>
   <si>
     <t>${table:record.items['SH-CM-10018-1']}</t>
+  </si>
+  <si>
+    <t>Roofing metal sheets (not less 0,45mm thickness, 1190 wide)</t>
+  </si>
+  <si>
+    <t>${table:record.items['SH-CM-10245']}</t>
   </si>
 </sst>
 </file>
@@ -2099,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE15C91-3DA2-449F-A7C4-9A49A11CFA57}">
-  <dimension ref="A1:BT12"/>
+  <dimension ref="A1:BU12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="43.1015625" customWidth="1"/>
@@ -2109,12 +2115,12 @@
     <col min="6" max="6" width="20.89453125" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="13.89453125" customWidth="1"/>
-    <col min="9" max="71" width="7.89453125" customWidth="1"/>
-    <col min="72" max="72" width="47.89453125" customWidth="1"/>
+    <col min="9" max="72" width="7.89453125" customWidth="1"/>
+    <col min="73" max="73" width="47.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="1:72" ht="27" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:73" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="1:73" ht="27" x14ac:dyDescent="0.85">
       <c r="A2" s="32" t="s">
         <v>0</v>
       </c>
@@ -2185,8 +2191,9 @@
       <c r="BR2" s="2"/>
       <c r="BS2" s="2"/>
       <c r="BT2" s="2"/>
-    </row>
-    <row r="3" spans="1:72" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="BU2" s="2"/>
+    </row>
+    <row r="3" spans="1:73" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="3"/>
       <c r="B3" s="36" t="s">
         <v>1</v>
@@ -2259,8 +2266,9 @@
       <c r="BR3" s="2"/>
       <c r="BS3" s="2"/>
       <c r="BT3" s="2"/>
-    </row>
-    <row r="4" spans="1:72" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="BU3" s="2"/>
+    </row>
+    <row r="4" spans="1:73" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A4" s="3"/>
       <c r="B4" s="36" t="s">
         <v>2</v>
@@ -2333,8 +2341,9 @@
       <c r="BR4" s="2"/>
       <c r="BS4" s="2"/>
       <c r="BT4" s="2"/>
-    </row>
-    <row r="5" spans="1:72" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="BU4" s="2"/>
+    </row>
+    <row r="5" spans="1:73" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A5" s="4"/>
       <c r="B5" s="39" t="s">
         <v>3</v>
@@ -2411,8 +2420,9 @@
       <c r="BR5" s="2"/>
       <c r="BS5" s="2"/>
       <c r="BT5" s="2"/>
-    </row>
-    <row r="6" spans="1:72" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="BU5" s="2"/>
+    </row>
+    <row r="6" spans="1:73" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A6" s="4"/>
       <c r="B6" s="39" t="s">
         <v>4</v>
@@ -2491,8 +2501,9 @@
       <c r="BR6" s="2"/>
       <c r="BS6" s="2"/>
       <c r="BT6" s="2"/>
-    </row>
-    <row r="7" spans="1:72" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="BU6" s="2"/>
+    </row>
+    <row r="7" spans="1:73" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A7" s="4"/>
       <c r="B7" s="39" t="s">
         <v>5</v>
@@ -2565,8 +2576,9 @@
       <c r="BR7" s="2"/>
       <c r="BS7" s="2"/>
       <c r="BT7" s="2"/>
-    </row>
-    <row r="8" spans="1:72" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="BU7" s="2"/>
+    </row>
+    <row r="8" spans="1:73" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A8" s="5"/>
       <c r="B8" s="35" t="s">
         <v>6</v>
@@ -2639,8 +2651,9 @@
       <c r="BR8" s="2"/>
       <c r="BS8" s="2"/>
       <c r="BT8" s="2"/>
-    </row>
-    <row r="9" spans="1:72" ht="28.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="BU8" s="2"/>
+    </row>
+    <row r="9" spans="1:73" ht="28.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="12" t="s">
         <v>7</v>
       </c>
@@ -2657,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="11">
-        <f t="shared" ref="I9:BS9" si="0">SUM(I$12:I$1000)</f>
+        <f t="shared" ref="I9:BT9" si="0">SUM(I$12:I$1000)</f>
         <v>0</v>
       </c>
       <c r="J9" s="11">
@@ -2908,8 +2921,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:72" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="BT9" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:73" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="14"/>
       <c r="B10" s="46" t="s">
         <v>8</v>
@@ -2985,9 +3002,10 @@
       <c r="BQ10" s="50"/>
       <c r="BR10" s="50"/>
       <c r="BS10" s="50"/>
-      <c r="BT10" s="29"/>
-    </row>
-    <row r="11" spans="1:72" ht="174" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="BT10" s="50"/>
+      <c r="BU10" s="29"/>
+    </row>
+    <row r="11" spans="1:73" ht="174" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="15" t="s">
         <v>9</v>
       </c>
@@ -3201,11 +3219,14 @@
       <c r="BS11" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="BT11" s="28" t="s">
+      <c r="BT11" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU11" s="28" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:72" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:73" ht="30" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="25" t="s">
         <v>64</v>
       </c>
@@ -3419,14 +3440,17 @@
       <c r="BS12" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="BT12" s="20" t="s">
+      <c r="BT12" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="BU12" s="20" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B10:G10"/>
-    <mergeCell ref="I10:BS10"/>
+    <mergeCell ref="I10:BT10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
